--- a/datasets/BDusage analysis.xlsx
+++ b/datasets/BDusage analysis.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>region</t>
   </si>
@@ -85,6 +85,12 @@
   </si>
   <si>
     <t>Ұлытау</t>
+  </si>
+  <si>
+    <t>Российская Федерация</t>
+  </si>
+  <si>
+    <t xml:space="preserve">г. Москва </t>
   </si>
 </sst>
 </file>
@@ -103,6 +109,8 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
@@ -148,12 +156,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -170,6 +181,1192 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Доля</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t> организаций использующих технологии сбора, анализа и обработки больших данных</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>BDusage!$J$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Республика Казахстан</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>BDusage!$K$1:$O$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>BDusage!$K$2:$O$2</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>7.2466979877670416E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.374769019754764E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.9258735212042601E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7483389909188501E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.7589106244334381E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3D3E-4973-B7E8-D14DFD0804DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>BDusage!$J$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Российская Федерация</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>BDusage!$K$1:$O$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>BDusage!$K$3:$O$3</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.31545899178382908</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.38136981217323951</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.190381535638696</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.104284615119604</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.8582692263443299E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3D3E-4973-B7E8-D14DFD0804DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>BDusage!$J$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>г. Алматы</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>BDusage!$K$1:$O$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>BDusage!$K$4:$O$4</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.5683154814330771E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.769695997800738E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.9915966386554619E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.6056660466447267E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.985493642802287E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3D3E-4973-B7E8-D14DFD0804DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>BDusage!$J$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>г. Москва </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>BDusage!$K$1:$O$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>BDusage!$K$5:$O$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.34650241970963491</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.40316222469791763</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.19860599890359459</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.1083338993411669</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.423704240666908E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-3D3E-4973-B7E8-D14DFD0804DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="244660255"/>
+        <c:axId val="244653599"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="244660255"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="244653599"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="244653599"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="244660255"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>428624</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -457,13 +1654,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="10" max="10" width="32.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -482,8 +1680,24 @@
       <c r="F1" s="1">
         <v>2025</v>
       </c>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="N1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="O1" s="1">
+        <v>2025</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -500,8 +1714,26 @@
       <c r="F2" s="2">
         <v>2.1100917431192662E-2</v>
       </c>
+      <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="3">
+        <v>7.2466979877670416E-3</v>
+      </c>
+      <c r="L2" s="3">
+        <v>1.374769019754764E-2</v>
+      </c>
+      <c r="M2" s="3">
+        <v>1.9258735212042601E-2</v>
+      </c>
+      <c r="N2" s="3">
+        <v>1.7483389909188501E-2</v>
+      </c>
+      <c r="O2" s="3">
+        <v>2.7589106244334381E-2</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -520,8 +1752,26 @@
       <c r="F3" s="2">
         <v>2.1258134490238612E-2</v>
       </c>
+      <c r="J3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0.31545899178382908</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0.38136981217323951</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0.190381535638696</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0.104284615119604</v>
+      </c>
+      <c r="O3" s="3">
+        <v>8.8582692263443299E-2</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -540,8 +1790,26 @@
       <c r="F4" s="2">
         <v>1.736299511665762E-2</v>
       </c>
+      <c r="J4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="3">
+        <v>1.5683154814330771E-2</v>
+      </c>
+      <c r="L4" s="3">
+        <v>2.769695997800738E-2</v>
+      </c>
+      <c r="M4" s="3">
+        <v>3.9915966386554619E-2</v>
+      </c>
+      <c r="N4" s="3">
+        <v>3.6056660466447267E-2</v>
+      </c>
+      <c r="O4" s="3">
+        <v>4.985493642802287E-2</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -560,8 +1828,26 @@
       <c r="F5" s="2">
         <v>1.292407108239095E-2</v>
       </c>
+      <c r="J5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0.34650241970963491</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0.40316222469791763</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0.19860599890359459</v>
+      </c>
+      <c r="N5" s="3">
+        <v>0.1083338993411669</v>
+      </c>
+      <c r="O5" s="3">
+        <v>9.423704240666908E-2</v>
+      </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -581,7 +1867,7 @@
         <v>2.536315425409269E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -601,7 +1887,7 @@
         <v>3.8768529076396809E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -621,7 +1907,7 @@
         <v>4.9685326266975822E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -639,7 +1925,7 @@
         <v>3.3416458852867828E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -659,7 +1945,7 @@
         <v>1.1810012836970481E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -679,7 +1965,7 @@
         <v>9.2510031208203301E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -699,7 +1985,7 @@
         <v>1.9182812200268561E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -719,7 +2005,7 @@
         <v>2.497808939526731E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -739,7 +2025,7 @@
         <v>2.9370300751879699E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -759,7 +2045,7 @@
         <v>2.3680056130503419E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -899,7 +2185,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3:B22">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -911,7 +2197,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C22">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -923,7 +2209,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D22">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -935,7 +2221,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E22">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -947,7 +2233,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F22">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -960,5 +2246,6 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/datasets/BDusage analysis.xlsx
+++ b/datasets/BDusage analysis.xlsx
@@ -206,10 +206,7 @@
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -217,14 +214,26 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ru-RU"/>
+              <a:rPr lang="ru-RU">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
               <a:t>Доля</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:rPr lang="ru-RU" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
               <a:t> организаций использующих технологии сбора, анализа и обработки больших данных</a:t>
             </a:r>
-            <a:endParaRPr lang="ru-RU"/>
+            <a:endParaRPr lang="ru-RU">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -244,10 +253,7 @@
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
